--- a/Data/EXCEL/Transfer/salemon/20240711/6874-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/6874-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B664EDF3-FE25-4AC3-8E44-B20A5CCB4E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1FEE17A-B42B-40C3-B2CF-38F0D18F0DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="290" windowWidth="18240" windowHeight="13390" xr2:uid="{2F1600FC-237A-4353-8A42-3C52AE5505AC}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{69BDA998-FDEB-4D42-AF69-B81BEAB745C0}"/>
   </bookViews>
   <sheets>
     <sheet name="6874-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1261,18 +1261,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{267B9541-565A-4BA6-AA83-68036D955735}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BD19D24-EE89-44D1-98AE-7C1323A06C82}">
   <dimension ref="A1:Q68"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="17" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="17" width="5.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1299,7 +1299,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1381,7 +1381,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1420,7 +1420,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1473,7 +1473,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="10">
         <v>45413</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>38.9</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1579,7 +1579,7 @@
         <v>41.8</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>45352</v>
       </c>
@@ -1632,7 +1632,7 @@
         <v>21.3</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="10">
         <v>45292</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>-2.81</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>8.26</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>45231</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>4.16</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="10">
         <v>45170</v>
       </c>
@@ -1950,7 +1950,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>2.79</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="10">
         <v>45108</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>1.54</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>-1.31</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="10">
         <v>45047</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>9.6999999999999993</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="10">
         <v>44986</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>2.87</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>120.7</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="10">
         <v>44927</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>218.6</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2427,7 +2427,7 @@
         <v>26.7</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="10">
         <v>44866</v>
       </c>
@@ -2480,7 +2480,7 @@
         <v>28.8</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="10">
         <v>44805</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>27.1</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>32.9</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="10">
         <v>44743</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>33.6</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>101.6</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="10">
         <v>44682</v>
       </c>
@@ -2798,7 +2798,7 @@
         <v>66.7</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2851,7 +2851,7 @@
         <v>66.8</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="10">
         <v>44621</v>
       </c>
@@ -2904,7 +2904,7 @@
         <v>72.3</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>8.39</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="10">
         <v>44562</v>
       </c>
@@ -3010,7 +3010,7 @@
         <v>-15.2</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3063,167 +3063,167 @@
         <v>61.4</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="10">
         <v>45413</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="10">
         <v>45352</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="10">
         <v>45292</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="10">
         <v>45231</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="10">
         <v>45170</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="10">
         <v>45108</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" s="10">
         <v>45047</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" s="10">
         <v>44986</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" s="10">
         <v>44927</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" s="10">
         <v>44866</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" s="10">
         <v>44805</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" s="10">
         <v>44743</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" s="10">
         <v>44682</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" s="10">
         <v>44621</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" s="10">
         <v>44562</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" s="5">
         <v>44531</v>
       </c>
